--- a/audit/results/pipeline_run/forecast/forecast_per_PLT.xlsx
+++ b/audit/results/pipeline_run/forecast/forecast_per_PLT.xlsx
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.2055898010730743</v>
+        <v>0.1981458961963654</v>
       </c>
     </row>
     <row r="3">
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.2014784663915634</v>
+        <v>0.1917186826467514</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.2051086276769638</v>
+        <v>0.1977371126413345</v>
       </c>
     </row>
     <row r="5">
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.2093458324670792</v>
+        <v>0.2050100713968277</v>
       </c>
     </row>
     <row r="6">
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.2144802957773209</v>
+        <v>0.2134234309196472</v>
       </c>
     </row>
     <row r="7">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.2147953510284424</v>
+        <v>0.2130265831947327</v>
       </c>
     </row>
     <row r="8">
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.2121152728796005</v>
+        <v>0.207306832075119</v>
       </c>
     </row>
     <row r="9">
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.2126018702983856</v>
+        <v>0.2084955722093582</v>
       </c>
     </row>
     <row r="10">
@@ -627,7 +627,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.2136121243238449</v>
+        <v>0.2109611034393311</v>
       </c>
     </row>
     <row r="11">
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.2143726199865341</v>
+        <v>0.2127841711044312</v>
       </c>
     </row>
     <row r="12">
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.2147867977619171</v>
+        <v>0.2136808186769485</v>
       </c>
     </row>
     <row r="13">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.2147235572338104</v>
+        <v>0.213355541229248</v>
       </c>
     </row>
     <row r="14">
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.2146432995796204</v>
+        <v>0.2131382822990417</v>
       </c>
     </row>
     <row r="15">
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.2148544490337372</v>
+        <v>0.2139088958501816</v>
       </c>
     </row>
     <row r="16">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.2150465846061707</v>
+        <v>0.2146125137805939</v>
       </c>
     </row>
     <row r="17">
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.2151601165533066</v>
+        <v>0.2150257527828217</v>
       </c>
     </row>
     <row r="18">
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.2152121961116791</v>
+        <v>0.2152214497327805</v>
       </c>
     </row>
     <row r="19">
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.2152323573827744</v>
+        <v>0.2153266966342926</v>
       </c>
     </row>
     <row r="20">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.2152666598558426</v>
+        <v>0.2155306786298752</v>
       </c>
     </row>
     <row r="21">
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.2153169810771942</v>
+        <v>0.2158208191394806</v>
       </c>
     </row>
     <row r="22">
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.2153531610965729</v>
+        <v>0.2160379886627197</v>
       </c>
     </row>
     <row r="23">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.2153752148151398</v>
+        <v>0.2161833047866821</v>
       </c>
     </row>
     <row r="24">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.2153896242380142</v>
+        <v>0.2162953764200211</v>
       </c>
     </row>
     <row r="25">
@@ -912,7 +912,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.215401753783226</v>
+        <v>0.216404527425766</v>
       </c>
     </row>
     <row r="26">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.2154143303632736</v>
+        <v>0.2165233492851257</v>
       </c>
     </row>
     <row r="27">
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.2154256701469421</v>
+        <v>0.2166344076395035</v>
       </c>
     </row>
     <row r="28">
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.2154336869716644</v>
+        <v>0.2167209684848785</v>
       </c>
     </row>
     <row r="29">
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.2154393941164017</v>
+        <v>0.2167913466691971</v>
       </c>
     </row>
     <row r="30">
@@ -1007,7 +1007,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.2154439389705658</v>
+        <v>0.2168545722961426</v>
       </c>
     </row>
     <row r="31">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.215447872877121</v>
+        <v>0.2169143110513687</v>
       </c>
     </row>
     <row r="32">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.2154513001441956</v>
+        <v>0.2169696390628815</v>
       </c>
     </row>
     <row r="33">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.2154540419578552</v>
+        <v>0.2170176059007645</v>
       </c>
     </row>
     <row r="34">
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.2154560834169388</v>
+        <v>0.2170580327510834</v>
       </c>
     </row>
     <row r="35">
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.2154577076435089</v>
+        <v>0.2170934826135635</v>
       </c>
     </row>
     <row r="36">
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.2154590338468552</v>
+        <v>0.2171256095170975</v>
       </c>
     </row>
     <row r="37">
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.2154601216316223</v>
+        <v>0.2171546220779419</v>
       </c>
     </row>
     <row r="38">
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>41.71794128417969</v>
+        <v>42.14241790771484</v>
       </c>
     </row>
     <row r="39">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>42.30929946899414</v>
+        <v>42.66729736328125</v>
       </c>
     </row>
     <row r="40">
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>39.01184844970703</v>
+        <v>39.17524719238281</v>
       </c>
     </row>
     <row r="41">
@@ -1216,7 +1216,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>33.61295318603516</v>
+        <v>33.72158050537109</v>
       </c>
     </row>
     <row r="42">
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>29.44555282592773</v>
+        <v>29.54876899719238</v>
       </c>
     </row>
     <row r="43">
@@ -1254,7 +1254,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>28.55472183227539</v>
+        <v>28.51874732971191</v>
       </c>
     </row>
     <row r="44">
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>29.19513702392578</v>
+        <v>28.95611572265625</v>
       </c>
     </row>
     <row r="45">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>29.35791969299316</v>
+        <v>29.27167892456055</v>
       </c>
     </row>
     <row r="46">
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>30.45405769348145</v>
+        <v>30.59482955932617</v>
       </c>
     </row>
     <row r="47">
@@ -1330,7 +1330,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>31.72622871398926</v>
+        <v>32.06243515014648</v>
       </c>
     </row>
     <row r="48">
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>32.51641845703125</v>
+        <v>32.97313690185547</v>
       </c>
     </row>
     <row r="49">
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>32.72043991088867</v>
+        <v>33.22615051269531</v>
       </c>
     </row>
     <row r="50">
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>32.66989135742188</v>
+        <v>33.15489196777344</v>
       </c>
     </row>
     <row r="51">
@@ -1406,7 +1406,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>32.53790664672852</v>
+        <v>32.92475509643555</v>
       </c>
     </row>
     <row r="52">
@@ -1425,7 +1425,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>32.24306488037109</v>
+        <v>32.51293182373047</v>
       </c>
     </row>
     <row r="53">
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>31.96423721313477</v>
+        <v>32.14188385009766</v>
       </c>
     </row>
     <row r="54">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>31.80010604858398</v>
+        <v>31.92726516723633</v>
       </c>
     </row>
     <row r="55">
@@ -1482,7 +1482,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>31.74516105651855</v>
+        <v>31.86203765869141</v>
       </c>
     </row>
     <row r="56">
@@ -1501,7 +1501,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>31.75167083740234</v>
+        <v>31.89072799682617</v>
       </c>
     </row>
     <row r="57">
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>31.79741668701172</v>
+        <v>31.97983741760254</v>
       </c>
     </row>
     <row r="58">
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>31.87009811401367</v>
+        <v>32.09817886352539</v>
       </c>
     </row>
     <row r="59">
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>31.93253135681152</v>
+        <v>32.19406509399414</v>
       </c>
     </row>
     <row r="60">
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>31.96938514709473</v>
+        <v>32.24724197387695</v>
       </c>
     </row>
     <row r="61">
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>31.98292922973633</v>
+        <v>32.26139831542969</v>
       </c>
     </row>
     <row r="62">
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>31.98040962219238</v>
+        <v>32.24808883666992</v>
       </c>
     </row>
     <row r="63">
@@ -1634,7 +1634,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>31.96728897094727</v>
+        <v>32.21859741210938</v>
       </c>
     </row>
     <row r="64">
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>31.94990921020508</v>
+        <v>32.18556976318359</v>
       </c>
     </row>
     <row r="65">
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>31.93564033508301</v>
+        <v>32.16055679321289</v>
       </c>
     </row>
     <row r="66">
@@ -1691,7 +1691,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>31.92713165283203</v>
+        <v>32.14741516113281</v>
       </c>
     </row>
     <row r="67">
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>31.92403793334961</v>
+        <v>32.14503479003906</v>
       </c>
     </row>
     <row r="68">
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>31.92500495910645</v>
+        <v>32.15026473999023</v>
       </c>
     </row>
     <row r="69">
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>31.9284610748291</v>
+        <v>32.15933990478516</v>
       </c>
     </row>
     <row r="70">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>31.93259429931641</v>
+        <v>32.16847229003906</v>
       </c>
     </row>
     <row r="71">
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>31.9359130859375</v>
+        <v>32.17501068115234</v>
       </c>
     </row>
     <row r="72">
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>31.9378833770752</v>
+        <v>32.17816925048828</v>
       </c>
     </row>
     <row r="73">
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>31.93855094909668</v>
+        <v>32.1783332824707</v>
       </c>
     </row>
     <row r="74">
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>53.96569061279297</v>
+        <v>54.60739517211914</v>
       </c>
     </row>
     <row r="75">
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>53.89773941040039</v>
+        <v>54.48634338378906</v>
       </c>
     </row>
     <row r="76">
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>53.38455200195312</v>
+        <v>53.46786499023438</v>
       </c>
     </row>
     <row r="77">
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>52.74752807617188</v>
+        <v>52.28712463378906</v>
       </c>
     </row>
     <row r="78">
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>52.611572265625</v>
+        <v>52.05686569213867</v>
       </c>
     </row>
     <row r="79">
@@ -1938,7 +1938,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>52.96492385864258</v>
+        <v>52.72470855712891</v>
       </c>
     </row>
     <row r="80">
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>53.34909439086914</v>
+        <v>53.39124298095703</v>
       </c>
     </row>
     <row r="81">
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>53.34562683105469</v>
+        <v>53.35125350952148</v>
       </c>
     </row>
     <row r="82">
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>53.33886337280273</v>
+        <v>53.30659484863281</v>
       </c>
     </row>
     <row r="83">
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>53.3337287902832</v>
+        <v>53.28704452514648</v>
       </c>
     </row>
     <row r="84">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>53.3337516784668</v>
+        <v>53.30298614501953</v>
       </c>
     </row>
     <row r="85">
@@ -2052,7 +2052,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>53.33688354492188</v>
+        <v>53.3314208984375</v>
       </c>
     </row>
     <row r="86">
@@ -2071,7 +2071,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>53.33916091918945</v>
+        <v>53.3463020324707</v>
       </c>
     </row>
     <row r="87">
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>53.33910369873047</v>
+        <v>53.34434509277344</v>
       </c>
     </row>
     <row r="88">
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>53.33903121948242</v>
+        <v>53.34332275390625</v>
       </c>
     </row>
     <row r="89">
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>53.33899688720703</v>
+        <v>53.34364700317383</v>
       </c>
     </row>
     <row r="90">
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>53.33900833129883</v>
+        <v>53.34477233886719</v>
       </c>
     </row>
     <row r="91">
@@ -2166,7 +2166,7 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>53.33903121948242</v>
+        <v>53.34572601318359</v>
       </c>
     </row>
     <row r="92">
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>53.33904647827148</v>
+        <v>53.34604263305664</v>
       </c>
     </row>
     <row r="93">
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>53.33904647827148</v>
+        <v>53.34598922729492</v>
       </c>
     </row>
     <row r="94">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>53.33903884887695</v>
+        <v>53.34599304199219</v>
       </c>
     </row>
     <row r="95">
@@ -2242,7 +2242,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>53.33903884887695</v>
+        <v>53.34603881835938</v>
       </c>
     </row>
     <row r="96">
@@ -2261,7 +2261,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>53.33904647827148</v>
+        <v>53.34608840942383</v>
       </c>
     </row>
     <row r="97">
@@ -2280,7 +2280,7 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>53.33904647827148</v>
+        <v>53.34611892700195</v>
       </c>
     </row>
     <row r="98">
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>53.33904647827148</v>
+        <v>53.34612274169922</v>
       </c>
     </row>
     <row r="99">
@@ -2318,7 +2318,7 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>53.33904647827148</v>
+        <v>53.34612274169922</v>
       </c>
     </row>
     <row r="100">
@@ -2337,7 +2337,7 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>53.33904647827148</v>
+        <v>53.34612655639648</v>
       </c>
     </row>
     <row r="101">
@@ -2356,7 +2356,7 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>53.33904647827148</v>
+        <v>53.34612655639648</v>
       </c>
     </row>
     <row r="102">
@@ -2375,7 +2375,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>53.33904647827148</v>
+        <v>53.34613037109375</v>
       </c>
     </row>
     <row r="103">
@@ -2394,7 +2394,7 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>53.33904647827148</v>
+        <v>53.34613037109375</v>
       </c>
     </row>
     <row r="104">
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>53.33904647827148</v>
+        <v>53.34613037109375</v>
       </c>
     </row>
     <row r="105">
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>53.33904647827148</v>
+        <v>53.34613037109375</v>
       </c>
     </row>
     <row r="106">
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>53.33904647827148</v>
+        <v>53.34613037109375</v>
       </c>
     </row>
     <row r="107">
@@ -2470,7 +2470,7 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>53.33904647827148</v>
+        <v>53.34613037109375</v>
       </c>
     </row>
     <row r="108">
@@ -2489,7 +2489,7 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>53.33904647827148</v>
+        <v>53.34613037109375</v>
       </c>
     </row>
     <row r="109">
@@ -2508,7 +2508,7 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>53.33904647827148</v>
+        <v>53.34613037109375</v>
       </c>
     </row>
     <row r="110">
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>30.10536766052246</v>
+        <v>30.06563186645508</v>
       </c>
     </row>
     <row r="111">
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>30.08872222900391</v>
+        <v>30.0448112487793</v>
       </c>
     </row>
     <row r="112">
@@ -2565,7 +2565,7 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>29.62514686584473</v>
+        <v>29.69511032104492</v>
       </c>
     </row>
     <row r="113">
@@ -2584,7 +2584,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>29.02863502502441</v>
+        <v>29.25302505493164</v>
       </c>
     </row>
     <row r="114">
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>28.69989585876465</v>
+        <v>29.0071907043457</v>
       </c>
     </row>
     <row r="115">
@@ -2622,7 +2622,7 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>28.80035781860352</v>
+        <v>29.06734275817871</v>
       </c>
     </row>
     <row r="116">
@@ -2641,7 +2641,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>29.06340599060059</v>
+        <v>29.25039291381836</v>
       </c>
     </row>
     <row r="117">
@@ -2660,7 +2660,7 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>29.08224487304688</v>
+        <v>29.25997734069824</v>
       </c>
     </row>
     <row r="118">
@@ -2679,7 +2679,7 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>29.10951232910156</v>
+        <v>29.27558898925781</v>
       </c>
     </row>
     <row r="119">
@@ -2698,7 +2698,7 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>29.12884521484375</v>
+        <v>29.28751945495605</v>
       </c>
     </row>
     <row r="120">
@@ -2717,7 +2717,7 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>29.13251304626465</v>
+        <v>29.29070472717285</v>
       </c>
     </row>
     <row r="121">
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>29.1252384185791</v>
+        <v>29.28734016418457</v>
       </c>
     </row>
     <row r="122">
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>29.11824607849121</v>
+        <v>29.28367805480957</v>
       </c>
     </row>
     <row r="123">
@@ -2774,7 +2774,7 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>29.11697769165039</v>
+        <v>29.28316116333008</v>
       </c>
     </row>
     <row r="124">
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>29.11588287353516</v>
+        <v>29.28264808654785</v>
       </c>
     </row>
     <row r="125">
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>29.11542129516602</v>
+        <v>29.28237915039062</v>
       </c>
     </row>
     <row r="126">
@@ -2831,7 +2831,7 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>29.11552810668945</v>
+        <v>29.28237152099609</v>
       </c>
     </row>
     <row r="127">
@@ -2850,7 +2850,7 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>29.1158447265625</v>
+        <v>29.2824821472168</v>
       </c>
     </row>
     <row r="128">
@@ -2869,7 +2869,7 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>29.11604690551758</v>
+        <v>29.28256034851074</v>
       </c>
     </row>
     <row r="129">
@@ -2888,7 +2888,7 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>29.11610794067383</v>
+        <v>29.28257942199707</v>
       </c>
     </row>
     <row r="130">
@@ -2907,7 +2907,7 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>29.11614227294922</v>
+        <v>29.28259658813477</v>
       </c>
     </row>
     <row r="131">
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>29.11614799499512</v>
+        <v>29.28260231018066</v>
       </c>
     </row>
     <row r="132">
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>29.11613845825195</v>
+        <v>29.28260231018066</v>
       </c>
     </row>
     <row r="133">
@@ -2964,7 +2964,7 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>29.11612510681152</v>
+        <v>29.28259658813477</v>
       </c>
     </row>
     <row r="134">
@@ -2983,7 +2983,7 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>29.11612129211426</v>
+        <v>29.28259468078613</v>
       </c>
     </row>
     <row r="135">
@@ -3002,7 +3002,7 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>29.11611557006836</v>
+        <v>29.28259468078613</v>
       </c>
     </row>
     <row r="136">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>29.11611557006836</v>
+        <v>29.28259468078613</v>
       </c>
     </row>
     <row r="137">
@@ -3040,7 +3040,7 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>29.11611557006836</v>
+        <v>29.28259468078613</v>
       </c>
     </row>
     <row r="138">
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>29.11611557006836</v>
+        <v>29.2825927734375</v>
       </c>
     </row>
     <row r="139">
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>29.11611938476562</v>
+        <v>29.2825927734375</v>
       </c>
     </row>
     <row r="140">
@@ -3097,7 +3097,7 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>29.11611938476562</v>
+        <v>29.28259468078613</v>
       </c>
     </row>
     <row r="141">
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>29.11611938476562</v>
+        <v>29.28259468078613</v>
       </c>
     </row>
     <row r="142">
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>29.11611938476562</v>
+        <v>29.28259468078613</v>
       </c>
     </row>
     <row r="143">
@@ -3154,7 +3154,7 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>29.11611938476562</v>
+        <v>29.28259468078613</v>
       </c>
     </row>
     <row r="144">
@@ -3173,7 +3173,7 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>29.11611938476562</v>
+        <v>29.28259468078613</v>
       </c>
     </row>
     <row r="145">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>29.11611938476562</v>
+        <v>29.28259468078613</v>
       </c>
     </row>
     <row r="146">
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>21.0440673828125</v>
+        <v>21.30466270446777</v>
       </c>
     </row>
     <row r="147">
@@ -3230,7 +3230,7 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>21.36346817016602</v>
+        <v>21.66031074523926</v>
       </c>
     </row>
     <row r="148">
@@ -3249,7 +3249,7 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>19.75210952758789</v>
+        <v>20.20112609863281</v>
       </c>
     </row>
     <row r="149">
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>17.03238296508789</v>
+        <v>17.70546722412109</v>
       </c>
     </row>
     <row r="150">
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>15.19434452056885</v>
+        <v>15.95350551605225</v>
       </c>
     </row>
     <row r="151">
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>14.97599411010742</v>
+        <v>15.74413585662842</v>
       </c>
     </row>
     <row r="152">
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>15.52635765075684</v>
+        <v>16.20712089538574</v>
       </c>
     </row>
     <row r="153">
@@ -3344,7 +3344,7 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>15.78923511505127</v>
+        <v>16.17560577392578</v>
       </c>
     </row>
     <row r="154">
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>16.43510055541992</v>
+        <v>16.46176338195801</v>
       </c>
     </row>
     <row r="155">
@@ -3382,7 +3382,7 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>17.0888500213623</v>
+        <v>16.82509422302246</v>
       </c>
     </row>
     <row r="156">
@@ -3401,7 +3401,7 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>17.40373802185059</v>
+        <v>17.04063034057617</v>
       </c>
     </row>
     <row r="157">
@@ -3420,7 +3420,7 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>17.38392066955566</v>
+        <v>17.08473777770996</v>
       </c>
     </row>
     <row r="158">
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>17.23705291748047</v>
+        <v>17.07318496704102</v>
       </c>
     </row>
     <row r="159">
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>17.08726119995117</v>
+        <v>17.07262992858887</v>
       </c>
     </row>
     <row r="160">
@@ -3477,7 +3477,7 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>16.89395904541016</v>
+        <v>17.02817726135254</v>
       </c>
     </row>
     <row r="161">
@@ -3496,7 +3496,7 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>16.75199890136719</v>
+        <v>16.97980880737305</v>
       </c>
     </row>
     <row r="162">
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>16.70499420166016</v>
+        <v>16.95139694213867</v>
       </c>
     </row>
     <row r="163">
@@ -3534,7 +3534,7 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>16.72782325744629</v>
+        <v>16.94111633300781</v>
       </c>
     </row>
     <row r="164">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>16.77689743041992</v>
+        <v>16.93781661987305</v>
       </c>
     </row>
     <row r="165">
@@ -3572,7 +3572,7 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>16.83009147644043</v>
+        <v>16.93807601928711</v>
       </c>
     </row>
     <row r="166">
@@ -3591,7 +3591,7 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>16.88015174865723</v>
+        <v>16.94412231445312</v>
       </c>
     </row>
     <row r="167">
@@ -3610,7 +3610,7 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>16.90843200683594</v>
+        <v>16.95038414001465</v>
       </c>
     </row>
     <row r="168">
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>16.91241836547852</v>
+        <v>16.95437240600586</v>
       </c>
     </row>
     <row r="169">
@@ -3648,7 +3648,7 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>16.90134620666504</v>
+        <v>16.9564037322998</v>
       </c>
     </row>
     <row r="170">
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>16.88508605957031</v>
+        <v>16.95733833312988</v>
       </c>
     </row>
     <row r="171">
@@ -3686,7 +3686,7 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>16.86931800842285</v>
+        <v>16.95735740661621</v>
       </c>
     </row>
     <row r="172">
@@ -3705,7 +3705,7 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>16.85757064819336</v>
+        <v>16.95661354064941</v>
       </c>
     </row>
     <row r="173">
@@ -3724,7 +3724,7 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>16.85271835327148</v>
+        <v>16.95581436157227</v>
       </c>
     </row>
     <row r="174">
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>16.85379791259766</v>
+        <v>16.95523834228516</v>
       </c>
     </row>
     <row r="175">
@@ -3762,7 +3762,7 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>16.8580493927002</v>
+        <v>16.95488166809082</v>
       </c>
     </row>
     <row r="176">
@@ -3781,7 +3781,7 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>16.86302947998047</v>
+        <v>16.95470237731934</v>
       </c>
     </row>
     <row r="177">
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>16.86721229553223</v>
+        <v>16.95467948913574</v>
       </c>
     </row>
     <row r="178">
@@ -3819,7 +3819,7 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>16.86970520019531</v>
+        <v>16.95476341247559</v>
       </c>
     </row>
     <row r="179">
@@ -3838,7 +3838,7 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>16.87026214599609</v>
+        <v>16.95486450195312</v>
       </c>
     </row>
     <row r="180">
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>16.86943435668945</v>
+        <v>16.95494842529297</v>
       </c>
     </row>
     <row r="181">
@@ -3876,7 +3876,7 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>16.86800384521484</v>
+        <v>16.95500564575195</v>
       </c>
     </row>
     <row r="182">
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>1.049232244491577</v>
+        <v>1.043514370918274</v>
       </c>
     </row>
     <row r="183">
@@ -3914,7 +3914,7 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>1.049323201179504</v>
+        <v>1.040735840797424</v>
       </c>
     </row>
     <row r="184">
@@ -3933,7 +3933,7 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>1.044426441192627</v>
+        <v>1.036025285720825</v>
       </c>
     </row>
     <row r="185">
@@ -3952,7 +3952,7 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>1.03996741771698</v>
+        <v>1.034098744392395</v>
       </c>
     </row>
     <row r="186">
@@ -3971,7 +3971,7 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1.037746548652649</v>
+        <v>1.036031007766724</v>
       </c>
     </row>
     <row r="187">
@@ -3990,7 +3990,7 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>1.043474435806274</v>
+        <v>1.044990301132202</v>
       </c>
     </row>
     <row r="188">
@@ -4009,7 +4009,7 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>1.054134488105774</v>
+        <v>1.058244705200195</v>
       </c>
     </row>
     <row r="189">
@@ -4028,7 +4028,7 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>1.053936004638672</v>
+        <v>1.058348536491394</v>
       </c>
     </row>
     <row r="190">
@@ -4047,7 +4047,7 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>1.053942680358887</v>
+        <v>1.059141397476196</v>
       </c>
     </row>
     <row r="191">
@@ -4066,7 +4066,7 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>1.054436206817627</v>
+        <v>1.060731768608093</v>
       </c>
     </row>
     <row r="192">
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1.055342316627502</v>
+        <v>1.062803626060486</v>
       </c>
     </row>
     <row r="193">
@@ -4104,7 +4104,7 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>1.05647337436676</v>
+        <v>1.064945220947266</v>
       </c>
     </row>
     <row r="194">
@@ -4123,7 +4123,7 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>1.057275176048279</v>
+        <v>1.066468000411987</v>
       </c>
     </row>
     <row r="195">
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>1.057413101196289</v>
+        <v>1.066947937011719</v>
       </c>
     </row>
     <row r="196">
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1.057604074478149</v>
+        <v>1.067542910575867</v>
       </c>
     </row>
     <row r="197">
@@ -4180,7 +4180,7 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>1.057823896408081</v>
+        <v>1.068169116973877</v>
       </c>
     </row>
     <row r="198">
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>1.058032155036926</v>
+        <v>1.068734407424927</v>
       </c>
     </row>
     <row r="199">
@@ -4218,7 +4218,7 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>1.058195829391479</v>
+        <v>1.069178700447083</v>
       </c>
     </row>
     <row r="200">
@@ -4237,7 +4237,7 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>1.058296322822571</v>
+        <v>1.069482326507568</v>
       </c>
     </row>
     <row r="201">
@@ -4256,7 +4256,7 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>1.058353185653687</v>
+        <v>1.06969141960144</v>
       </c>
     </row>
     <row r="202">
@@ -4275,7 +4275,7 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>1.058408617973328</v>
+        <v>1.069891810417175</v>
       </c>
     </row>
     <row r="203">
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>1.058457016944885</v>
+        <v>1.070066094398499</v>
       </c>
     </row>
     <row r="204">
@@ -4313,7 +4313,7 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>1.058495044708252</v>
+        <v>1.070206522941589</v>
       </c>
     </row>
     <row r="205">
@@ -4332,7 +4332,7 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>1.058522462844849</v>
+        <v>1.070313692092896</v>
       </c>
     </row>
     <row r="206">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>1.058541536331177</v>
+        <v>1.070395350456238</v>
       </c>
     </row>
     <row r="207">
@@ -4370,7 +4370,7 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>1.058555841445923</v>
+        <v>1.070461392402649</v>
       </c>
     </row>
     <row r="208">
@@ -4389,7 +4389,7 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>1.058567881584167</v>
+        <v>1.070517778396606</v>
       </c>
     </row>
     <row r="209">
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>1.058577418327332</v>
+        <v>1.070563912391663</v>
       </c>
     </row>
     <row r="210">
@@ -4427,7 +4427,7 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>1.058584451675415</v>
+        <v>1.070600152015686</v>
       </c>
     </row>
     <row r="211">
@@ -4446,7 +4446,7 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>1.058589696884155</v>
+        <v>1.070628762245178</v>
       </c>
     </row>
     <row r="212">
@@ -4465,7 +4465,7 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>1.05859375</v>
+        <v>1.070651650428772</v>
       </c>
     </row>
     <row r="213">
@@ -4484,7 +4484,7 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>1.058596849441528</v>
+        <v>1.070670366287231</v>
       </c>
     </row>
     <row r="214">
@@ -4503,7 +4503,7 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>1.058599352836609</v>
+        <v>1.070685625076294</v>
       </c>
     </row>
     <row r="215">
@@ -4522,7 +4522,7 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>1.058601140975952</v>
+        <v>1.070698022842407</v>
       </c>
     </row>
     <row r="216">
@@ -4541,7 +4541,7 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>1.058602452278137</v>
+        <v>1.070707678794861</v>
       </c>
     </row>
     <row r="217">
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>1.058603525161743</v>
+        <v>1.070715665817261</v>
       </c>
     </row>
     <row r="218">
@@ -4579,7 +4579,7 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>1.129010081291199</v>
+        <v>1.160460352897644</v>
       </c>
     </row>
     <row r="219">
@@ -4598,7 +4598,7 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>1.14285671710968</v>
+        <v>1.193167328834534</v>
       </c>
     </row>
     <row r="220">
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>1.132822513580322</v>
+        <v>1.189282059669495</v>
       </c>
     </row>
     <row r="221">
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>1.111667513847351</v>
+        <v>1.163278341293335</v>
       </c>
     </row>
     <row r="222">
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>1.085559487342834</v>
+        <v>1.123060703277588</v>
       </c>
     </row>
     <row r="223">
@@ -4674,7 +4674,7 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>1.077556967735291</v>
+        <v>1.108652353286743</v>
       </c>
     </row>
     <row r="224">
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>1.083499431610107</v>
+        <v>1.116925954818726</v>
       </c>
     </row>
     <row r="225">
@@ -4712,7 +4712,7 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>1.081797361373901</v>
+        <v>1.116760969161987</v>
       </c>
     </row>
     <row r="226">
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>1.079582929611206</v>
+        <v>1.115631818771362</v>
       </c>
     </row>
     <row r="227">
@@ -4750,7 +4750,7 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>1.077720046043396</v>
+        <v>1.114299535751343</v>
       </c>
     </row>
     <row r="228">
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>1.076582908630371</v>
+        <v>1.113325834274292</v>
       </c>
     </row>
     <row r="229">
@@ -4788,7 +4788,7 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>1.076300859451294</v>
+        <v>1.11314845085144</v>
       </c>
     </row>
     <row r="230">
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>1.076253533363342</v>
+        <v>1.113282799720764</v>
       </c>
     </row>
     <row r="231">
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>1.075994968414307</v>
+        <v>1.113232254981995</v>
       </c>
     </row>
     <row r="232">
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>1.075791597366333</v>
+        <v>1.113172292709351</v>
       </c>
     </row>
     <row r="233">
@@ -4864,7 +4864,7 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>1.075661182403564</v>
+        <v>1.113126397132874</v>
       </c>
     </row>
     <row r="234">
@@ -4883,7 +4883,7 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>1.075591564178467</v>
+        <v>1.113104104995728</v>
       </c>
     </row>
     <row r="235">
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>1.075557947158813</v>
+        <v>1.113101243972778</v>
       </c>
     </row>
     <row r="236">
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>1.075531721115112</v>
+        <v>1.113101720809937</v>
       </c>
     </row>
     <row r="237">
@@ -4940,7 +4940,7 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>1.075506448745728</v>
+        <v>1.113098621368408</v>
       </c>
     </row>
     <row r="238">
@@ -4959,7 +4959,7 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>1.075489640235901</v>
+        <v>1.113096356391907</v>
       </c>
     </row>
     <row r="239">
@@ -4978,7 +4978,7 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>1.07547914981842</v>
+        <v>1.113095045089722</v>
       </c>
     </row>
     <row r="240">
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>1.075472950935364</v>
+        <v>1.113094449043274</v>
       </c>
     </row>
     <row r="241">
@@ -5016,7 +5016,7 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>1.075468897819519</v>
+        <v>1.113094329833984</v>
       </c>
     </row>
     <row r="242">
@@ -5035,7 +5035,7 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>1.075465798377991</v>
+        <v>1.113094329833984</v>
       </c>
     </row>
     <row r="243">
@@ -5054,7 +5054,7 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>1.075463533401489</v>
+        <v>1.113094210624695</v>
       </c>
     </row>
     <row r="244">
@@ -5073,7 +5073,7 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>1.075461983680725</v>
+        <v>1.113094091415405</v>
       </c>
     </row>
     <row r="245">
@@ -5092,7 +5092,7 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>1.075461149215698</v>
+        <v>1.113094091415405</v>
       </c>
     </row>
     <row r="246">
@@ -5111,7 +5111,7 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>1.075460433959961</v>
+        <v>1.113094091415405</v>
       </c>
     </row>
     <row r="247">
@@ -5130,7 +5130,7 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>1.075459957122803</v>
+        <v>1.113094091415405</v>
       </c>
     </row>
     <row r="248">
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>1.075459599494934</v>
+        <v>1.113094091415405</v>
       </c>
     </row>
     <row r="249">
@@ -5168,7 +5168,7 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>1.075459361076355</v>
+        <v>1.113094091415405</v>
       </c>
     </row>
     <row r="250">
@@ -5187,7 +5187,7 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>1.075459241867065</v>
+        <v>1.113094091415405</v>
       </c>
     </row>
     <row r="251">
@@ -5206,7 +5206,7 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>1.075459241867065</v>
+        <v>1.113094091415405</v>
       </c>
     </row>
     <row r="252">
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>1.075459122657776</v>
+        <v>1.113094091415405</v>
       </c>
     </row>
     <row r="253">
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>1.075459122657776</v>
+        <v>1.113094091415405</v>
       </c>
     </row>
   </sheetData>

--- a/audit/results/pipeline_run/forecast/forecast_per_PLT.xlsx
+++ b/audit/results/pipeline_run/forecast/forecast_per_PLT.xlsx
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.1981458961963654</v>
+        <v>0.2144300490617752</v>
       </c>
     </row>
     <row r="3">
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.1917186826467514</v>
+        <v>0.2153859883546829</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.1977371126413345</v>
+        <v>0.2171100974082947</v>
       </c>
     </row>
     <row r="5">
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.2050100713968277</v>
+        <v>0.219426229596138</v>
       </c>
     </row>
     <row r="6">
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.2134234309196472</v>
+        <v>0.2222553193569183</v>
       </c>
     </row>
     <row r="7">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.2130265831947327</v>
+        <v>0.222990944981575</v>
       </c>
     </row>
     <row r="8">
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.207306832075119</v>
+        <v>0.2251304686069489</v>
       </c>
     </row>
     <row r="9">
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.2084955722093582</v>
+        <v>0.2245320826768875</v>
       </c>
     </row>
     <row r="10">
@@ -627,7 +627,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.2109611034393311</v>
+        <v>0.220474436879158</v>
       </c>
     </row>
     <row r="11">
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.2127841711044312</v>
+        <v>0.2148774862289429</v>
       </c>
     </row>
     <row r="12">
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.2136808186769485</v>
+        <v>0.2122810631990433</v>
       </c>
     </row>
     <row r="13">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.213355541229248</v>
+        <v>0.2136063128709793</v>
       </c>
     </row>
     <row r="14">
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.2131382822990417</v>
+        <v>0.2161350399255753</v>
       </c>
     </row>
     <row r="15">
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.2139088958501816</v>
+        <v>0.2162344753742218</v>
       </c>
     </row>
     <row r="16">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.2146125137805939</v>
+        <v>0.2162699997425079</v>
       </c>
     </row>
     <row r="17">
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.2150257527828217</v>
+        <v>0.2162244617938995</v>
       </c>
     </row>
     <row r="18">
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.2152214497327805</v>
+        <v>0.2160866558551788</v>
       </c>
     </row>
     <row r="19">
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.2153266966342926</v>
+        <v>0.2158483564853668</v>
       </c>
     </row>
     <row r="20">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.2155306786298752</v>
+        <v>0.2155856192111969</v>
       </c>
     </row>
     <row r="21">
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.2158208191394806</v>
+        <v>0.2152575105428696</v>
       </c>
     </row>
     <row r="22">
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.2160379886627197</v>
+        <v>0.2149581611156464</v>
       </c>
     </row>
     <row r="23">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.2161833047866821</v>
+        <v>0.2147993147373199</v>
       </c>
     </row>
     <row r="24">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.2162953764200211</v>
+        <v>0.2148245871067047</v>
       </c>
     </row>
     <row r="25">
@@ -912,7 +912,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.216404527425766</v>
+        <v>0.2149278223514557</v>
       </c>
     </row>
     <row r="26">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.2165233492851257</v>
+        <v>0.2149778008460999</v>
       </c>
     </row>
     <row r="27">
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.2166344076395035</v>
+        <v>0.2149383425712585</v>
       </c>
     </row>
     <row r="28">
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.2167209684848785</v>
+        <v>0.2148932069540024</v>
       </c>
     </row>
     <row r="29">
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.2167913466691971</v>
+        <v>0.2148455083370209</v>
       </c>
     </row>
     <row r="30">
@@ -1007,7 +1007,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.2168545722961426</v>
+        <v>0.2147986590862274</v>
       </c>
     </row>
     <row r="31">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.2169143110513687</v>
+        <v>0.2147561311721802</v>
       </c>
     </row>
     <row r="32">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.2169696390628815</v>
+        <v>0.2147214114665985</v>
       </c>
     </row>
     <row r="33">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.2170176059007645</v>
+        <v>0.2146951705217361</v>
       </c>
     </row>
     <row r="34">
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.2170580327510834</v>
+        <v>0.2146793603897095</v>
       </c>
     </row>
     <row r="35">
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.2170934826135635</v>
+        <v>0.2146726548671722</v>
       </c>
     </row>
     <row r="36">
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.2171256095170975</v>
+        <v>0.2146702110767365</v>
       </c>
     </row>
     <row r="37">
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.2171546220779419</v>
+        <v>0.2146659046411514</v>
       </c>
     </row>
     <row r="38">
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>42.14241790771484</v>
+        <v>41.79047775268555</v>
       </c>
     </row>
     <row r="39">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>42.66729736328125</v>
+        <v>42.07587814331055</v>
       </c>
     </row>
     <row r="40">
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>39.17524719238281</v>
+        <v>38.64453887939453</v>
       </c>
     </row>
     <row r="41">
@@ -1216,7 +1216,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>33.72158050537109</v>
+        <v>33.22151565551758</v>
       </c>
     </row>
     <row r="42">
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>29.54876899719238</v>
+        <v>29.27628517150879</v>
       </c>
     </row>
     <row r="43">
@@ -1254,7 +1254,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>28.51874732971191</v>
+        <v>28.97376823425293</v>
       </c>
     </row>
     <row r="44">
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>28.95611572265625</v>
+        <v>30.37478828430176</v>
       </c>
     </row>
     <row r="45">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>29.27167892456055</v>
+        <v>30.54631805419922</v>
       </c>
     </row>
     <row r="46">
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>30.59482955932617</v>
+        <v>31.20702934265137</v>
       </c>
     </row>
     <row r="47">
@@ -1330,7 +1330,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>32.06243515014648</v>
+        <v>31.86470222473145</v>
       </c>
     </row>
     <row r="48">
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>32.97313690185547</v>
+        <v>32.18814468383789</v>
       </c>
     </row>
     <row r="49">
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>33.22615051269531</v>
+        <v>32.19218826293945</v>
       </c>
     </row>
     <row r="50">
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>33.15489196777344</v>
+        <v>32.10548782348633</v>
       </c>
     </row>
     <row r="51">
@@ -1406,7 +1406,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>32.92475509643555</v>
+        <v>32.04892730712891</v>
       </c>
     </row>
     <row r="52">
@@ -1425,7 +1425,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>32.51293182373047</v>
+        <v>31.95703506469727</v>
       </c>
     </row>
     <row r="53">
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>32.14188385009766</v>
+        <v>31.88684272766113</v>
       </c>
     </row>
     <row r="54">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>31.92726516723633</v>
+        <v>31.8570728302002</v>
       </c>
     </row>
     <row r="55">
@@ -1482,7 +1482,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>31.86203765869141</v>
+        <v>31.85513877868652</v>
       </c>
     </row>
     <row r="56">
@@ -1501,7 +1501,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>31.89072799682617</v>
+        <v>31.86243057250977</v>
       </c>
     </row>
     <row r="57">
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>31.97983741760254</v>
+        <v>31.87196731567383</v>
       </c>
     </row>
     <row r="58">
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>32.09817886352539</v>
+        <v>31.8831672668457</v>
       </c>
     </row>
     <row r="59">
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>32.19406509399414</v>
+        <v>31.89066886901855</v>
       </c>
     </row>
     <row r="60">
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>32.24724197387695</v>
+        <v>31.8937931060791</v>
       </c>
     </row>
     <row r="61">
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>32.26139831542969</v>
+        <v>31.89415550231934</v>
       </c>
     </row>
     <row r="62">
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>32.24808883666992</v>
+        <v>31.89329719543457</v>
       </c>
     </row>
     <row r="63">
@@ -1634,7 +1634,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>32.21859741210938</v>
+        <v>31.8919734954834</v>
       </c>
     </row>
     <row r="64">
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>32.18556976318359</v>
+        <v>31.89067268371582</v>
       </c>
     </row>
     <row r="65">
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>32.16055679321289</v>
+        <v>31.88984489440918</v>
       </c>
     </row>
     <row r="66">
@@ -1691,7 +1691,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>32.14741516113281</v>
+        <v>31.88949966430664</v>
       </c>
     </row>
     <row r="67">
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>32.14503479003906</v>
+        <v>31.88945198059082</v>
       </c>
     </row>
     <row r="68">
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>32.15026473999023</v>
+        <v>31.88956451416016</v>
       </c>
     </row>
     <row r="69">
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>32.15933990478516</v>
+        <v>31.88973236083984</v>
       </c>
     </row>
     <row r="70">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>32.16847229003906</v>
+        <v>31.88988304138184</v>
       </c>
     </row>
     <row r="71">
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>32.17501068115234</v>
+        <v>31.88997650146484</v>
       </c>
     </row>
     <row r="72">
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>32.17816925048828</v>
+        <v>31.89001846313477</v>
       </c>
     </row>
     <row r="73">
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>32.1783332824707</v>
+        <v>31.89001846313477</v>
       </c>
     </row>
     <row r="74">
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>54.60739517211914</v>
+        <v>52.78004837036133</v>
       </c>
     </row>
     <row r="75">
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>54.48634338378906</v>
+        <v>63.9907341003418</v>
       </c>
     </row>
     <row r="76">
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>53.46786499023438</v>
+        <v>62.66918563842773</v>
       </c>
     </row>
     <row r="77">
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>52.28712463378906</v>
+        <v>61.82566833496094</v>
       </c>
     </row>
     <row r="78">
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>52.05686569213867</v>
+        <v>56.911865234375</v>
       </c>
     </row>
     <row r="79">
@@ -1938,7 +1938,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>52.72470855712891</v>
+        <v>46.00775146484375</v>
       </c>
     </row>
     <row r="80">
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>53.39124298095703</v>
+        <v>44.06991577148438</v>
       </c>
     </row>
     <row r="81">
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>53.35125350952148</v>
+        <v>47.40839767456055</v>
       </c>
     </row>
     <row r="82">
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>53.30659484863281</v>
+        <v>51.68097305297852</v>
       </c>
     </row>
     <row r="83">
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>53.28704452514648</v>
+        <v>54.97122955322266</v>
       </c>
     </row>
     <row r="84">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>53.30298614501953</v>
+        <v>56.58944702148438</v>
       </c>
     </row>
     <row r="85">
@@ -2052,7 +2052,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>53.3314208984375</v>
+        <v>56.04106140136719</v>
       </c>
     </row>
     <row r="86">
@@ -2071,7 +2071,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>53.3463020324707</v>
+        <v>52.92650985717773</v>
       </c>
     </row>
     <row r="87">
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>53.34434509277344</v>
+        <v>50.18373489379883</v>
       </c>
     </row>
     <row r="88">
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>53.34332275390625</v>
+        <v>49.39379501342773</v>
       </c>
     </row>
     <row r="89">
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>53.34364700317383</v>
+        <v>50.27697372436523</v>
       </c>
     </row>
     <row r="90">
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>53.34477233886719</v>
+        <v>51.86906814575195</v>
       </c>
     </row>
     <row r="91">
@@ -2166,7 +2166,7 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>53.34572601318359</v>
+        <v>53.26568984985352</v>
       </c>
     </row>
     <row r="92">
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>53.34604263305664</v>
+        <v>53.88470840454102</v>
       </c>
     </row>
     <row r="93">
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>53.34598922729492</v>
+        <v>53.47042465209961</v>
       </c>
     </row>
     <row r="94">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>53.34599304199219</v>
+        <v>52.42555618286133</v>
       </c>
     </row>
     <row r="95">
@@ -2242,7 +2242,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>53.34603881835938</v>
+        <v>51.49842071533203</v>
       </c>
     </row>
     <row r="96">
@@ -2261,7 +2261,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>53.34608840942383</v>
+        <v>51.17664337158203</v>
       </c>
     </row>
     <row r="97">
@@ -2280,7 +2280,7 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>53.34611892700195</v>
+        <v>51.4684944152832</v>
       </c>
     </row>
     <row r="98">
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>53.34612274169922</v>
+        <v>52.06586456298828</v>
       </c>
     </row>
     <row r="99">
@@ -2318,7 +2318,7 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>53.34612274169922</v>
+        <v>52.59916305541992</v>
       </c>
     </row>
     <row r="100">
@@ -2337,7 +2337,7 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>53.34612655639648</v>
+        <v>52.80897903442383</v>
       </c>
     </row>
     <row r="101">
@@ -2356,7 +2356,7 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>53.34612655639648</v>
+        <v>52.64665985107422</v>
       </c>
     </row>
     <row r="102">
@@ -2375,7 +2375,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>53.34613037109375</v>
+        <v>52.27543258666992</v>
       </c>
     </row>
     <row r="103">
@@ -2394,7 +2394,7 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>53.34613037109375</v>
+        <v>51.94441986083984</v>
       </c>
     </row>
     <row r="104">
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>53.34613037109375</v>
+        <v>51.82357788085938</v>
       </c>
     </row>
     <row r="105">
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>53.34613037109375</v>
+        <v>51.92670822143555</v>
       </c>
     </row>
     <row r="106">
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>53.34613037109375</v>
+        <v>52.14694595336914</v>
       </c>
     </row>
     <row r="107">
@@ -2470,7 +2470,7 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>53.34613037109375</v>
+        <v>52.34314727783203</v>
       </c>
     </row>
     <row r="108">
@@ -2489,7 +2489,7 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>53.34613037109375</v>
+        <v>52.41788482666016</v>
       </c>
     </row>
     <row r="109">
@@ -2508,7 +2508,7 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>53.34613037109375</v>
+        <v>52.35743713378906</v>
       </c>
     </row>
     <row r="110">
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>30.06563186645508</v>
+        <v>37.20394897460938</v>
       </c>
     </row>
     <row r="111">
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>30.0448112487793</v>
+        <v>37.52354049682617</v>
       </c>
     </row>
     <row r="112">
@@ -2565,7 +2565,7 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>29.69511032104492</v>
+        <v>34.53264236450195</v>
       </c>
     </row>
     <row r="113">
@@ -2584,7 +2584,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>29.25302505493164</v>
+        <v>30.14791870117188</v>
       </c>
     </row>
     <row r="114">
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>29.0071907043457</v>
+        <v>26.8221607208252</v>
       </c>
     </row>
     <row r="115">
@@ -2622,7 +2622,7 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>29.06734275817871</v>
+        <v>25.56826782226562</v>
       </c>
     </row>
     <row r="116">
@@ -2641,7 +2641,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>29.25039291381836</v>
+        <v>25.40634918212891</v>
       </c>
     </row>
     <row r="117">
@@ -2660,7 +2660,7 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>29.25997734069824</v>
+        <v>26.07307434082031</v>
       </c>
     </row>
     <row r="118">
@@ -2679,7 +2679,7 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>29.27558898925781</v>
+        <v>27.83245849609375</v>
       </c>
     </row>
     <row r="119">
@@ -2698,7 +2698,7 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>29.28751945495605</v>
+        <v>29.7409839630127</v>
       </c>
     </row>
     <row r="120">
@@ -2717,7 +2717,7 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>29.29070472717285</v>
+        <v>31.08707427978516</v>
       </c>
     </row>
     <row r="121">
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>29.28734016418457</v>
+        <v>31.67799758911133</v>
       </c>
     </row>
     <row r="122">
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>29.28367805480957</v>
+        <v>31.63325691223145</v>
       </c>
     </row>
     <row r="123">
@@ -2774,7 +2774,7 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>29.28316116333008</v>
+        <v>31.04755592346191</v>
       </c>
     </row>
     <row r="124">
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>29.28264808654785</v>
+        <v>30.13585662841797</v>
       </c>
     </row>
     <row r="125">
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>29.28237915039062</v>
+        <v>29.27560424804688</v>
       </c>
     </row>
     <row r="126">
@@ -2831,7 +2831,7 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>29.28237152099609</v>
+        <v>28.6981086730957</v>
       </c>
     </row>
     <row r="127">
@@ -2850,7 +2850,7 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>29.2824821472168</v>
+        <v>28.47729873657227</v>
       </c>
     </row>
     <row r="128">
@@ -2869,7 +2869,7 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>29.28256034851074</v>
+        <v>28.58761596679688</v>
       </c>
     </row>
     <row r="129">
@@ -2888,7 +2888,7 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>29.28257942199707</v>
+        <v>28.94241523742676</v>
       </c>
     </row>
     <row r="130">
@@ -2907,7 +2907,7 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>29.28259658813477</v>
+        <v>29.39480781555176</v>
       </c>
     </row>
     <row r="131">
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>29.28260231018066</v>
+        <v>29.79018402099609</v>
       </c>
     </row>
     <row r="132">
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>29.28260231018066</v>
+        <v>30.03469276428223</v>
       </c>
     </row>
     <row r="133">
@@ -2964,7 +2964,7 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>29.28259658813477</v>
+        <v>30.0977954864502</v>
       </c>
     </row>
     <row r="134">
@@ -2983,7 +2983,7 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>29.28259468078613</v>
+        <v>30.00099182128906</v>
       </c>
     </row>
     <row r="135">
@@ -3002,7 +3002,7 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>29.28259468078613</v>
+        <v>29.80333709716797</v>
       </c>
     </row>
     <row r="136">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>29.28259468078613</v>
+        <v>29.58146858215332</v>
       </c>
     </row>
     <row r="137">
@@ -3040,7 +3040,7 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>29.28259468078613</v>
+        <v>29.40229606628418</v>
       </c>
     </row>
     <row r="138">
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>29.2825927734375</v>
+        <v>29.30453681945801</v>
       </c>
     </row>
     <row r="139">
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>29.2825927734375</v>
+        <v>29.29680252075195</v>
       </c>
     </row>
     <row r="140">
@@ -3097,7 +3097,7 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>29.28259468078613</v>
+        <v>29.36203765869141</v>
       </c>
     </row>
     <row r="141">
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>29.28259468078613</v>
+        <v>29.46684265136719</v>
       </c>
     </row>
     <row r="142">
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>29.28259468078613</v>
+        <v>29.57380485534668</v>
       </c>
     </row>
     <row r="143">
@@ -3154,7 +3154,7 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>29.28259468078613</v>
+        <v>29.65319633483887</v>
       </c>
     </row>
     <row r="144">
@@ -3173,7 +3173,7 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>29.28259468078613</v>
+        <v>29.68948173522949</v>
       </c>
     </row>
     <row r="145">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>29.28259468078613</v>
+        <v>29.68211936950684</v>
       </c>
     </row>
     <row r="146">
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>21.30466270446777</v>
+        <v>21.48100471496582</v>
       </c>
     </row>
     <row r="147">
@@ -3230,7 +3230,7 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>21.66031074523926</v>
+        <v>21.74174308776855</v>
       </c>
     </row>
     <row r="148">
@@ -3249,7 +3249,7 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>20.20112609863281</v>
+        <v>20.56599807739258</v>
       </c>
     </row>
     <row r="149">
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>17.70546722412109</v>
+        <v>18.2559700012207</v>
       </c>
     </row>
     <row r="150">
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>15.95350551605225</v>
+        <v>16.37749099731445</v>
       </c>
     </row>
     <row r="151">
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>15.74413585662842</v>
+        <v>16.25071334838867</v>
       </c>
     </row>
     <row r="152">
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>16.20712089538574</v>
+        <v>16.9067554473877</v>
       </c>
     </row>
     <row r="153">
@@ -3344,7 +3344,7 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>16.17560577392578</v>
+        <v>16.74679756164551</v>
       </c>
     </row>
     <row r="154">
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>16.46176338195801</v>
+        <v>16.8489933013916</v>
       </c>
     </row>
     <row r="155">
@@ -3382,7 +3382,7 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>16.82509422302246</v>
+        <v>17.0616626739502</v>
       </c>
     </row>
     <row r="156">
@@ -3401,7 +3401,7 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>17.04063034057617</v>
+        <v>17.20982360839844</v>
       </c>
     </row>
     <row r="157">
@@ -3420,7 +3420,7 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>17.08473777770996</v>
+        <v>17.23784637451172</v>
       </c>
     </row>
     <row r="158">
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>17.07318496704102</v>
+        <v>17.23270606994629</v>
       </c>
     </row>
     <row r="159">
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>17.07262992858887</v>
+        <v>17.25822639465332</v>
       </c>
     </row>
     <row r="160">
@@ -3477,7 +3477,7 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>17.02817726135254</v>
+        <v>17.25614738464355</v>
       </c>
     </row>
     <row r="161">
@@ -3496,7 +3496,7 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>16.97980880737305</v>
+        <v>17.24363327026367</v>
       </c>
     </row>
     <row r="162">
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>16.95139694213867</v>
+        <v>17.23478889465332</v>
       </c>
     </row>
     <row r="163">
@@ -3534,7 +3534,7 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>16.94111633300781</v>
+        <v>17.23205184936523</v>
       </c>
     </row>
     <row r="164">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>16.93781661987305</v>
+        <v>17.2301082611084</v>
       </c>
     </row>
     <row r="165">
@@ -3572,7 +3572,7 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>16.93807601928711</v>
+        <v>17.22730445861816</v>
       </c>
     </row>
     <row r="166">
@@ -3591,7 +3591,7 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>16.94412231445312</v>
+        <v>17.22682952880859</v>
       </c>
     </row>
     <row r="167">
@@ -3610,7 +3610,7 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>16.95038414001465</v>
+        <v>17.22723960876465</v>
       </c>
     </row>
     <row r="168">
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>16.95437240600586</v>
+        <v>17.22756004333496</v>
       </c>
     </row>
     <row r="169">
@@ -3648,7 +3648,7 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>16.9564037322998</v>
+        <v>17.22770500183105</v>
       </c>
     </row>
     <row r="170">
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>16.95733833312988</v>
+        <v>17.22791862487793</v>
       </c>
     </row>
     <row r="171">
@@ -3686,7 +3686,7 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>16.95735740661621</v>
+        <v>17.2281551361084</v>
       </c>
     </row>
     <row r="172">
@@ -3705,7 +3705,7 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>16.95661354064941</v>
+        <v>17.22823143005371</v>
       </c>
     </row>
     <row r="173">
@@ -3724,7 +3724,7 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>16.95581436157227</v>
+        <v>17.22824287414551</v>
       </c>
     </row>
     <row r="174">
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>16.95523834228516</v>
+        <v>17.22825241088867</v>
       </c>
     </row>
     <row r="175">
@@ -3762,7 +3762,7 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>16.95488166809082</v>
+        <v>17.2282543182373</v>
       </c>
     </row>
     <row r="176">
@@ -3781,7 +3781,7 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>16.95470237731934</v>
+        <v>17.22824096679688</v>
       </c>
     </row>
     <row r="177">
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>16.95467948913574</v>
+        <v>17.22822570800781</v>
       </c>
     </row>
     <row r="178">
@@ -3819,7 +3819,7 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>16.95476341247559</v>
+        <v>17.22821998596191</v>
       </c>
     </row>
     <row r="179">
@@ -3838,7 +3838,7 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>16.95486450195312</v>
+        <v>17.22821426391602</v>
       </c>
     </row>
     <row r="180">
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>16.95494842529297</v>
+        <v>17.22821235656738</v>
       </c>
     </row>
     <row r="181">
@@ -3876,7 +3876,7 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>16.95500564575195</v>
+        <v>17.22821044921875</v>
       </c>
     </row>
     <row r="182">
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>1.043514370918274</v>
+        <v>1.12479031085968</v>
       </c>
     </row>
     <row r="183">
@@ -3914,7 +3914,7 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>1.040735840797424</v>
+        <v>1.146151185035706</v>
       </c>
     </row>
     <row r="184">
@@ -3933,7 +3933,7 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>1.036025285720825</v>
+        <v>1.176853775978088</v>
       </c>
     </row>
     <row r="185">
@@ -3952,7 +3952,7 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>1.034098744392395</v>
+        <v>1.193889498710632</v>
       </c>
     </row>
     <row r="186">
@@ -3971,7 +3971,7 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1.036031007766724</v>
+        <v>1.218555927276611</v>
       </c>
     </row>
     <row r="187">
@@ -3990,7 +3990,7 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>1.044990301132202</v>
+        <v>1.250014781951904</v>
       </c>
     </row>
     <row r="188">
@@ -4009,7 +4009,7 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>1.058244705200195</v>
+        <v>1.289179086685181</v>
       </c>
     </row>
     <row r="189">
@@ -4028,7 +4028,7 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>1.058348536491394</v>
+        <v>1.328487753868103</v>
       </c>
     </row>
     <row r="190">
@@ -4047,7 +4047,7 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>1.059141397476196</v>
+        <v>1.359382748603821</v>
       </c>
     </row>
     <row r="191">
@@ -4066,7 +4066,7 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>1.060731768608093</v>
+        <v>1.390078783035278</v>
       </c>
     </row>
     <row r="192">
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1.062803626060486</v>
+        <v>1.423931002616882</v>
       </c>
     </row>
     <row r="193">
@@ -4104,7 +4104,7 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>1.064945220947266</v>
+        <v>1.472423672676086</v>
       </c>
     </row>
     <row r="194">
@@ -4123,7 +4123,7 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>1.066468000411987</v>
+        <v>1.530065298080444</v>
       </c>
     </row>
     <row r="195">
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>1.066947937011719</v>
+        <v>1.558256506919861</v>
       </c>
     </row>
     <row r="196">
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1.067542910575867</v>
+        <v>1.586719036102295</v>
       </c>
     </row>
     <row r="197">
@@ -4180,7 +4180,7 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>1.068169116973877</v>
+        <v>1.614228248596191</v>
       </c>
     </row>
     <row r="198">
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>1.068734407424927</v>
+        <v>1.642266511917114</v>
       </c>
     </row>
     <row r="199">
@@ -4218,7 +4218,7 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>1.069178700447083</v>
+        <v>1.669736742973328</v>
       </c>
     </row>
     <row r="200">
@@ -4237,7 +4237,7 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>1.069482326507568</v>
+        <v>1.695799112319946</v>
       </c>
     </row>
     <row r="201">
@@ -4256,7 +4256,7 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>1.06969141960144</v>
+        <v>1.719699144363403</v>
       </c>
     </row>
     <row r="202">
@@ -4275,7 +4275,7 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>1.069891810417175</v>
+        <v>1.741528987884521</v>
       </c>
     </row>
     <row r="203">
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>1.070066094398499</v>
+        <v>1.762093305587769</v>
       </c>
     </row>
     <row r="204">
@@ -4313,7 +4313,7 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>1.070206522941589</v>
+        <v>1.781363725662231</v>
       </c>
     </row>
     <row r="205">
@@ -4332,7 +4332,7 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>1.070313692092896</v>
+        <v>1.79904580116272</v>
       </c>
     </row>
     <row r="206">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>1.070395350456238</v>
+        <v>1.814068794250488</v>
       </c>
     </row>
     <row r="207">
@@ -4370,7 +4370,7 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>1.070461392402649</v>
+        <v>1.825964570045471</v>
       </c>
     </row>
     <row r="208">
@@ -4389,7 +4389,7 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>1.070517778396606</v>
+        <v>1.836963653564453</v>
       </c>
     </row>
     <row r="209">
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>1.070563912391663</v>
+        <v>1.847034811973572</v>
       </c>
     </row>
     <row r="210">
@@ -4427,7 +4427,7 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>1.070600152015686</v>
+        <v>1.856223464012146</v>
       </c>
     </row>
     <row r="211">
@@ -4446,7 +4446,7 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>1.070628762245178</v>
+        <v>1.864473819732666</v>
       </c>
     </row>
     <row r="212">
@@ -4465,7 +4465,7 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>1.070651650428772</v>
+        <v>1.871801137924194</v>
       </c>
     </row>
     <row r="213">
@@ -4484,7 +4484,7 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>1.070670366287231</v>
+        <v>1.878267407417297</v>
       </c>
     </row>
     <row r="214">
@@ -4503,7 +4503,7 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>1.070685625076294</v>
+        <v>1.883971571922302</v>
       </c>
     </row>
     <row r="215">
@@ -4522,7 +4522,7 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>1.070698022842407</v>
+        <v>1.888998866081238</v>
       </c>
     </row>
     <row r="216">
@@ -4541,7 +4541,7 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>1.070707678794861</v>
+        <v>1.893384456634521</v>
       </c>
     </row>
     <row r="217">
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>1.070715665817261</v>
+        <v>1.897165417671204</v>
       </c>
     </row>
     <row r="218">
@@ -4579,7 +4579,7 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>1.160460352897644</v>
+        <v>1.12996518611908</v>
       </c>
     </row>
     <row r="219">
@@ -4598,7 +4598,7 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>1.193167328834534</v>
+        <v>1.163098335266113</v>
       </c>
     </row>
     <row r="220">
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>1.189282059669495</v>
+        <v>1.202515363693237</v>
       </c>
     </row>
     <row r="221">
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>1.163278341293335</v>
+        <v>1.211594820022583</v>
       </c>
     </row>
     <row r="222">
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>1.123060703277588</v>
+        <v>1.222086548805237</v>
       </c>
     </row>
     <row r="223">
@@ -4674,7 +4674,7 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>1.108652353286743</v>
+        <v>1.232492208480835</v>
       </c>
     </row>
     <row r="224">
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>1.116925954818726</v>
+        <v>1.244624137878418</v>
       </c>
     </row>
     <row r="225">
@@ -4712,7 +4712,7 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>1.116760969161987</v>
+        <v>1.247006773948669</v>
       </c>
     </row>
     <row r="226">
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>1.115631818771362</v>
+        <v>1.225769639015198</v>
       </c>
     </row>
     <row r="227">
@@ -4750,7 +4750,7 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>1.114299535751343</v>
+        <v>1.195793986320496</v>
       </c>
     </row>
     <row r="228">
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>1.113325834274292</v>
+        <v>1.164592504501343</v>
       </c>
     </row>
     <row r="229">
@@ -4788,7 +4788,7 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>1.11314845085144</v>
+        <v>1.155294895172119</v>
       </c>
     </row>
     <row r="230">
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>1.113282799720764</v>
+        <v>1.160769462585449</v>
       </c>
     </row>
     <row r="231">
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>1.113232254981995</v>
+        <v>1.16125500202179</v>
       </c>
     </row>
     <row r="232">
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>1.113172292709351</v>
+        <v>1.16126811504364</v>
       </c>
     </row>
     <row r="233">
@@ -4864,7 +4864,7 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>1.113126397132874</v>
+        <v>1.160832762718201</v>
       </c>
     </row>
     <row r="234">
@@ -4883,7 +4883,7 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>1.113104104995728</v>
+        <v>1.160248875617981</v>
       </c>
     </row>
     <row r="235">
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>1.113101243972778</v>
+        <v>1.159549832344055</v>
       </c>
     </row>
     <row r="236">
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>1.113101720809937</v>
+        <v>1.158773303031921</v>
       </c>
     </row>
     <row r="237">
@@ -4940,7 +4940,7 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>1.113098621368408</v>
+        <v>1.157935261726379</v>
       </c>
     </row>
     <row r="238">
@@ -4959,7 +4959,7 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>1.113096356391907</v>
+        <v>1.15713107585907</v>
       </c>
     </row>
     <row r="239">
@@ -4978,7 +4978,7 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>1.113095045089722</v>
+        <v>1.156544923782349</v>
       </c>
     </row>
     <row r="240">
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>1.113094449043274</v>
+        <v>1.156228184700012</v>
       </c>
     </row>
     <row r="241">
@@ -5016,7 +5016,7 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>1.113094329833984</v>
+        <v>1.156166911125183</v>
       </c>
     </row>
     <row r="242">
@@ -5035,7 +5035,7 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>1.113094329833984</v>
+        <v>1.156172394752502</v>
       </c>
     </row>
     <row r="243">
@@ -5054,7 +5054,7 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>1.113094210624695</v>
+        <v>1.156127333641052</v>
       </c>
     </row>
     <row r="244">
@@ -5073,7 +5073,7 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>1.113094091415405</v>
+        <v>1.156076073646545</v>
       </c>
     </row>
     <row r="245">
@@ -5092,7 +5092,7 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>1.113094091415405</v>
+        <v>1.156024575233459</v>
       </c>
     </row>
     <row r="246">
@@ -5111,7 +5111,7 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>1.113094091415405</v>
+        <v>1.155977368354797</v>
       </c>
     </row>
     <row r="247">
@@ -5130,7 +5130,7 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>1.113094091415405</v>
+        <v>1.155936479568481</v>
       </c>
     </row>
     <row r="248">
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>1.113094091415405</v>
+        <v>1.155902743339539</v>
       </c>
     </row>
     <row r="249">
@@ -5168,7 +5168,7 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>1.113094091415405</v>
+        <v>1.155876994132996</v>
       </c>
     </row>
     <row r="250">
@@ -5187,7 +5187,7 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>1.113094091415405</v>
+        <v>1.155858755111694</v>
       </c>
     </row>
     <row r="251">
@@ -5206,7 +5206,7 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>1.113094091415405</v>
+        <v>1.155847668647766</v>
       </c>
     </row>
     <row r="252">
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>1.113094091415405</v>
+        <v>1.155841708183289</v>
       </c>
     </row>
     <row r="253">
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>1.113094091415405</v>
+        <v>1.155838251113892</v>
       </c>
     </row>
   </sheetData>
